--- a/entertainment_forms/047_fort_unit_job_application--entertainment_forms.xlsx
+++ b/entertainment_forms/047_fort_unit_job_application--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>job_type_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Job Type</t>
+          <t>Job Type 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>job_status_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Job Status</t>
+          <t>Job Status 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_description_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Job Description 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>last_name_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Last Name 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,114 +1335,114 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
